--- a/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23520" windowHeight="11670"/>
+    <workbookView windowWidth="24720" windowHeight="9705"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
   <si>
     <t>0普通模型和角色一样1定制模型</t>
   </si>
@@ -1153,8 +1153,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:S7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="C1:S9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -1436,6 +1436,112 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="3:19">
+      <c r="C8" s="5">
+        <v>44003</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3003</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>50</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" s="5">
+        <v>202</v>
+      </c>
+      <c r="P8" s="5">
+        <v>177</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1.49</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2000</v>
+      </c>
+      <c r="S8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="3:19">
+      <c r="C9" s="5">
+        <v>44004</v>
+      </c>
+      <c r="D9" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3004</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>50</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O9" s="5">
+        <v>202</v>
+      </c>
+      <c r="P9" s="5">
+        <v>177</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>1.49</v>
+      </c>
+      <c r="R9" s="5">
+        <v>2000</v>
+      </c>
+      <c r="S9" s="5">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24720" windowHeight="9705"/>
+    <workbookView windowWidth="22500" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="45">
   <si>
     <t>0普通模型和角色一样1定制模型</t>
   </si>
@@ -145,7 +145,7 @@
     <t>float</t>
   </si>
   <si>
-    <t>10501001,0,0,0,50001001</t>
+    <t>Monster44001</t>
   </si>
   <si>
     <t>7,10</t>
@@ -161,6 +161,12 @@
   </si>
   <si>
     <t>Monster44002</t>
+  </si>
+  <si>
+    <t>Monster44003</t>
+  </si>
+  <si>
+    <t>Monster44004</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1347,7 @@
         <v>3001</v>
       </c>
       <c r="F6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>37</v>
@@ -1447,10 +1453,10 @@
         <v>3003</v>
       </c>
       <c r="F8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
@@ -1500,10 +1506,10 @@
         <v>3004</v>
       </c>
       <c r="F9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H9" s="5">
         <v>1</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
   <si>
     <t>0普通模型和角色一样1定制模型</t>
   </si>
@@ -1159,7 +1159,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:S9"/>
+  <dimension ref="C1:S10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -1548,6 +1548,59 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" spans="3:19">
+      <c r="C10" s="5">
+        <v>44005</v>
+      </c>
+      <c r="D10" s="5">
+        <v>10001</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3005</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>50</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O10" s="5">
+        <v>202</v>
+      </c>
+      <c r="P10" s="5">
+        <v>177</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>1.49</v>
+      </c>
+      <c r="R10" s="5">
+        <v>2000</v>
+      </c>
+      <c r="S10" s="5">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
